--- a/public/data/contract_baggage.xlsx
+++ b/public/data/contract_baggage.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>421d42eb-4038-41ee-b868-fd1837b72a3d</v>
+        <v>ebf84ed7-404c-479b-a30e-1fcf2043e458</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,13 +447,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>d4f349cb-d5e6-40bf-a1d7-72ab7c36c4c8</v>
+        <v>f4b71d83-02be-49cb-b4c1-e701e3ba7d75</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -470,200 +470,200 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>7533ebe9-05e7-4244-94bf-76d4f1e3c004</v>
+        <v>a595f4a3-19ff-4c4a-b0cf-e411f2fea647</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
         <v>Checked baggage</v>
       </c>
       <c r="F4" t="str">
-        <v>25 kg per adult</v>
+        <v>30 kg per adult</v>
       </c>
       <c r="G4" t="str">
-        <v>Hard cases accepted</v>
+        <v>Charter premium allowance</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>efb0f62b-4518-4a06-a602-5584a7612ff0</v>
+        <v>4ef5ecb6-bdef-4b62-bd64-ad87c752f4d4</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E5" t="str">
-        <v>Checked baggage</v>
+        <v>Hand baggage</v>
       </c>
       <c r="F5" t="str">
-        <v>30 kg per adult</v>
+        <v>7 kg per person</v>
       </c>
       <c r="G5" t="str">
-        <v>Charter allows heavier luggage</v>
+        <v>Charter cabin allowance</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3f370286-0528-4f00-82e9-124662a11b0d</v>
+        <v>b25d4e3e-35b0-4865-a04b-833a0fca6ea4</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E6" t="str">
-        <v>Excess baggage</v>
+        <v>Checked baggage</v>
       </c>
       <c r="F6" t="str">
-        <v>$5 per kg</v>
+        <v>25 kg per adult</v>
       </c>
       <c r="G6" t="str">
-        <v>Payable at check-in counter</v>
+        <v>Hard cases accepted</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>df750ee9-d5c0-4d69-b110-1a98481415eb</v>
+        <v>a48c83bb-311a-44e4-8b5f-27b07bef98fd</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E7" t="str">
-        <v>Checked baggage</v>
+        <v>Hand baggage</v>
       </c>
       <c r="F7" t="str">
-        <v>25 kg per adult</v>
+        <v>5 kg per person</v>
       </c>
       <c r="G7" t="str">
-        <v>Standard allowance</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>0ea1db0e-deb6-4b8d-b5a3-492c39d050c1</v>
+        <v>e93222ce-dcf6-4234-adb0-31dd414c0ef8</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E8" t="str">
         <v>Checked baggage</v>
       </c>
       <c r="F8" t="str">
-        <v>25 kg per adult</v>
+        <v>32 kg per adult</v>
       </c>
       <c r="G8" t="str">
-        <v>Soft bags strongly preferred</v>
+        <v>Soneva charter allows heavier luggage</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>fc286c6a-9e85-472a-9997-98c28a80bd13</v>
+        <v>f5d96080-3668-47b2-a60f-d73b0944e3ae</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E9" t="str">
-        <v>Hand baggage</v>
+        <v>Excess baggage</v>
       </c>
       <c r="F9" t="str">
-        <v>5 kg per person</v>
+        <v>$5 per kg</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>Payable at check-in counter</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>911a1aa7-c111-4634-9827-260444ed988e</v>
+        <v>c518b1dd-b9b7-4a52-8a17-45a812d9d5b1</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E10" t="str">
-        <v>Excess baggage</v>
+        <v>Checked baggage</v>
       </c>
       <c r="F10" t="str">
-        <v>$6 per kg</v>
+        <v>25 kg per adult</v>
       </c>
       <c r="G10" t="str">
-        <v>Subject to availability</v>
+        <v>Standard seaplane allowance</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>6a81f861-e802-45d2-9d49-df5ab0d03471</v>
+        <v>5b529956-79b4-4b2b-8266-67e23d1985e4</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E11" t="str">
         <v>Checked baggage</v>
       </c>
       <c r="F11" t="str">
-        <v>32 kg per adult</v>
+        <v>35 kg per adult</v>
       </c>
       <c r="G11" t="str">
-        <v>Charter premium allowance</v>
+        <v>Signed charter premium</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>4e1f7bc7-fc37-434e-8767-329fa6069c2e</v>
+        <v>70839751-266c-4c0a-a4b7-701c2cda8b8d</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E12" t="str">
         <v>Sports equipment</v>
@@ -672,44 +672,44 @@
         <v>Pre-approval required</v>
       </c>
       <c r="G12" t="str">
-        <v>Surfboards, dive gear etc.</v>
+        <v>Diving, surfing gear</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>bf1873d2-0505-4386-a253-b97f2f98d42c</v>
+        <v>e1f87001-39e6-46d6-accf-fe9a925247e0</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E13" t="str">
         <v>Checked baggage</v>
       </c>
       <c r="F13" t="str">
-        <v>20 kg per adult</v>
+        <v>25 kg per adult</v>
       </c>
       <c r="G13" t="str">
-        <v>Speedboat transfer</v>
+        <v>Standard allowance</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>970e2002-bbb5-4ab4-b918-9ef35b6fa835</v>
+        <v>1135d22a-aa39-4df2-848d-5e463e8d9a96</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
-        <v>CTR-010-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E14" t="str">
         <v>Checked baggage</v>
@@ -718,12 +718,311 @@
         <v>30 kg per adult</v>
       </c>
       <c r="G14" t="str">
+        <v>Charter allowance</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>40720f58-4a75-4a0a-8846-c89690fa8f95</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F15" t="str">
+        <v>25 kg per adult</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Soft bags strongly preferred</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>6c0758d5-f93f-4595-9fe9-2a30ac4ad5f5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Hand baggage</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5 kg per person</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>bd98f0f5-2019-431b-ad27-06b8cb46c7a2</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Excess baggage</v>
+      </c>
+      <c r="F17" t="str">
+        <v>$6 per kg</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Subject to availability</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>d9e4d391-a7d3-4394-91b8-b2d96216610d</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30 kg per adult</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Charter allowance</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>56ea5719-698a-4272-9552-aebd73b58b20</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F19" t="str">
+        <v>35 kg per adult</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Signed charter premium</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2b5e6c82-6300-4430-a9f3-3559ad99d019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20 kg per adult</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Speedboat weight restrictions</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>0085bbdb-0f5e-447c-9275-dccbfcec455b</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F21" t="str">
+        <v>25 kg per adult</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Standard seaplane</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3ca3ea1a-7866-48d0-81f5-1204004af70b</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F22" t="str">
+        <v>32 kg per adult</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Charter premium allowance</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>5e392451-e0df-46b0-9b5c-44a9ec8ce1af</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D23" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Sports equipment</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Pre-approval required</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Surfboards, dive gear etc.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>4fcc4a2e-5c24-4bf7-9bdb-603fa8fbb47b</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D24" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F24" t="str">
+        <v>25 kg per adult</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Standard seaplane</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>208744eb-a9e0-4e31-87de-5781a9c7d970</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D25" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F25" t="str">
+        <v>20 kg per adult</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Speedboat transfer</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>c8f3f8fc-b6c8-4c2b-9be5-4ba70553bc3d</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D26" t="str">
+        <v>CTR-010-001</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F26" t="str">
+        <v>30 kg per adult</v>
+      </c>
+      <c r="G26" t="str">
         <v>Soneva charter allowance</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>a3eac25c-d454-4c3a-b148-eefd4de523d7</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D27" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Checked baggage</v>
+      </c>
+      <c r="F27" t="str">
+        <v>25 kg per adult</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Standard seaplane</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G27"/>
   </ignoredErrors>
 </worksheet>
 </file>